--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -29,8 +29,11 @@
     <sheet name="SERIES" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="CLUBS" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="META" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -38,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +56,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,11 +96,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12248,7 +12266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12302,6 +12320,129 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>CLUB_S2010_11_0048</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2010_11_0232 'Jiskra Humpolec B' prev→CLUB_S2009_10_0117 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2010_11_0233 'HC Šternberk (OLO)' ROZBITÝ prev CLUB_S2009_10_0185 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2010_11_0241 'HC Grewis Plumov (OLO)' ROZBITÝ prev CLUB_S2009_10_0185 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2010_11_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2010_11_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2010_11_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0021</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2010_11_0021 'Baráž o Extraligu' (L15, parent=NODE_S2010_11_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0028</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2010_11_0028 'Baráž o I.ligu' (L25, parent=NODE_S2010_11_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0043</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2010_11_0043 'O postup do I.ligy' (L25, parent=NODE_S2010_11_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -15900,8 +16041,6 @@
         </is>
       </c>
     </row>
-    <row r="85"/>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -15981,7 +16120,6 @@
         </is>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
@@ -33427,6 +33565,259 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0232</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0232 'Jiskra Humpolec B' prev→CLUB_S2009_10_0117 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0233</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0233 'HC Šternberk (OLO)' ROZBITÝ prev CLUB_S2009_10_0185 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0241</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0241 'HC Grewis Plumov (OLO)' ROZBITÝ prev CLUB_S2009_10_0185 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0031</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0032</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0033</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0021</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2010_11_0021 'Baráž o Extraligu' (L15, parent=NODE_S2010_11_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0028</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2010_11_0028 'Baráž o I.ligu' (L25, parent=NODE_S2010_11_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0043</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2010_11_0043 'O postup do I.ligy' (L25, parent=NODE_S2010_11_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -32,7 +32,7 @@
     <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10000,11 +10000,6 @@
           <t>CLUB_S2010_11_0233</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0185</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>setrval</t>
@@ -10627,11 +10622,6 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>CLUB_S2010_11_0241</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0185</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -12266,7 +12256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12326,7 +12316,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S2010_11_0232 'Jiskra Humpolec B' prev→CLUB_S2009_10_0117 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12338,7 +12328,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S2010_11_0233 'HC Šternberk (OLO)' ROZBITÝ prev CLUB_S2009_10_0185 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -12350,7 +12340,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S2010_11_0241 'HC Grewis Plumov (OLO)' ROZBITÝ prev CLUB_S2009_10_0185 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12362,7 +12352,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2010_11_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12374,7 +12364,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2010_11_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12386,7 +12376,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2010_11_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -12396,14 +12386,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S2010_11_0021</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2010_11_0021 'Baráž o Extraligu' (L15, parent=NODE_S2010_11_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12413,14 +12398,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NODE_S2010_11_0028</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2010_11_0028 'Baráž o I.ligu' (L25, parent=NODE_S2010_11_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12430,17 +12410,411 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NODE_S2010_11_0043</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2010_11_0043 'O postup do I.ligy' (L25, parent=NODE_S2010_11_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Merend' → 'Nový Knín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2009_10_0117 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0030</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0031</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0032</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -16041,6 +16415,8 @@
         </is>
       </c>
     </row>
+    <row r="85"/>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -16071,6 +16447,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0001</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -16083,6 +16464,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0003</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -16095,6 +16481,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0003</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -16107,6 +16498,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0037</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -16120,6 +16516,7 @@
         </is>
       </c>
     </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
@@ -23628,12 +24025,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -23838,12 +24235,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -24174,12 +24571,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -24216,12 +24613,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -24342,12 +24739,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -24594,12 +24991,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň.</t>
+          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň. || TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sportovní klub Kadaň</t>
+          <t>Kadaň</t>
         </is>
       </c>
     </row>
@@ -24982,12 +25379,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -25241,12 +25638,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -25530,12 +25927,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -25572,12 +25969,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Klatovy = SHC Maso Brejcha Klatovy (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Maso Brejcha** = sponzor (řeznictví). city Klatovy.</t>
+          <t>Klatovy = SHC Maso Brejcha Klatovy (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Maso Brejcha** = sponzor (řeznictví). city Klatovy. || TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SHC Maso Brejcha Klatovy</t>
+          <t>Klatovy</t>
         </is>
       </c>
     </row>
@@ -25656,12 +26053,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -25866,12 +26263,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Česká Lípa = HC Predators Česká Lípa (Wiki D42 - registr ustavy 04/2026). Liberecky kraj. Post-revolucni anglicky nazev. city Česká Lípa.</t>
+          <t>Česká Lípa = HC Predators Česká Lípa (Wiki D42 - registr ustavy 04/2026). Liberecky kraj. Post-revolucni anglicky nazev. city Česká Lípa. || TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Predators Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -25950,12 +26347,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>SC Kolín</t>
         </is>
       </c>
     </row>
@@ -26081,12 +26478,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -26679,12 +27076,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -27015,12 +27412,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný.</t>
+          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný. || TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>UHK LEV Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -27057,12 +27454,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -27692,12 +28089,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Nový Knín = SK Nový Knín – Merend (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Příbram). city Nový Knín.</t>
+          <t>Nový Knín = SK Nový Knín – Merend (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Příbram). city Nový Knín. || TBD: city 'Merend' → 'Nový Knín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Merend</t>
+          <t>Nový Knín</t>
         </is>
       </c>
     </row>
@@ -27818,12 +28215,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -27860,12 +28257,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -28490,12 +28887,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -28981,12 +29378,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Plzeň = SKP Rapid Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **SKP** = Sportovni klub policie. city Plzeň.</t>
+          <t>Plzeň = SKP Rapid Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **SKP** = Sportovni klub policie. city Plzeň. || TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>SKP Rapid Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -29593,12 +29990,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -30454,12 +30851,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Cheb = PSK 96 Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **PSK 96** = Policejni sportovni klub zalozen 1996. city Cheb.</t>
+          <t>Cheb = PSK 96 Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **PSK 96** = Policejni sportovni klub zalozen 1996. city Cheb. || TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>PSK 96 Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -30528,12 +30925,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Cheb = IHT Brimstones Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. Post-revolucni anglicky nazev. city Cheb.</t>
+          <t>Cheb = IHT Brimstones Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. Post-revolucni anglicky nazev. city Cheb. || TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>IHT Brimstones Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -30995,12 +31392,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Česká Lípa = HC Predators Česká Lípa (Wiki D42 - registr ustavy 04/2026). Liberecky kraj. Post-revolucni anglicky nazev. city Česká Lípa.</t>
+          <t>Česká Lípa = HC Predators Česká Lípa (Wiki D42 - registr ustavy 04/2026). Liberecky kraj. Post-revolucni anglicky nazev. city Česká Lípa. || TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Predators Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -31541,12 +31938,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka.</t>
+          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka. || TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>BK JTC Nová Paka</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -31709,12 +32106,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -32542,14 +32939,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0185</t>
-        </is>
-      </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Smart fix prev: 51/52 0390 (neexistuje) → 0388. Oprava city z „Chronotechna Šternberk" na „Šternberk". Identity transition: 51/52 měl chybně „Sokol Chronotechnika" — opravený název „Chronotechna" (správný název závodu, potvrzeno Pavlem) — retroaktivně opraveno i v 51/52. || Šternberk = Dukla/Chronotechnika Šternberk (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Chronotechna = vyrobce hodinek. Dukla = vojensky. city Šternberk.</t>
+          <t>Smart fix prev: 51/52 0390 (neexistuje) → 0388. Oprava city z „Chronotechna Šternberk" na „Šternberk". Identity transition: 51/52 měl chybně „Sokol Chronotechnika" — opravený název „Chronotechna" (správný název závodu, potvrzeno Pavlem) — retroaktivně opraveno i v 51/52. || Šternberk = Dukla/Chronotechnika Šternberk (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Chronotechna = vyrobce hodinek. Dukla = vojensky. city Šternberk. || TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -32591,12 +32983,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -32883,14 +33275,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>CLUB_S2009_10_0185</t>
-        </is>
-      </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Plumlov = HC Grewis Plumov (Wiki D42 - registr ustavy 04/2026). Olomoucky kraj (okres Prostějov). '(OLO)' = Olomouc. PARSING CHYBA: 'Plumov' = preklep z 'Plumlov'. city Plumlov.</t>
+          <t>Plumlov = HC Grewis Plumov (Wiki D42 - registr ustavy 04/2026). Olomoucky kraj (okres Prostějov). '(OLO)' = Olomouc. PARSING CHYBA: 'Plumov' = preklep z 'Plumlov'. city Plumlov. || TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -33315,12 +33702,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -33571,11 +33958,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -33620,21 +34007,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0232</t>
+          <t>CLUB_S2010_11_0001</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0232 'Jiskra Humpolec B' prev→CLUB_S2009_10_0117 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -33642,21 +34027,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0233</t>
+          <t>CLUB_S2010_11_0006</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0233 'HC Šternberk (OLO)' ROZBITÝ prev CLUB_S2009_10_0185 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -33664,21 +34047,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0241</t>
+          <t>CLUB_S2010_11_0014</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0241 'HC Grewis Plumov (OLO)' ROZBITÝ prev CLUB_S2009_10_0185 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -33686,21 +34067,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0031</t>
+          <t>CLUB_S2010_11_0015</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -33708,21 +34087,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0032</t>
+          <t>CLUB_S2010_11_0018</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -33730,21 +34107,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0033</t>
+          <t>CLUB_S2010_11_0024</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -33752,21 +34127,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NODE_S2010_11_0021</t>
+          <t>CLUB_S2010_11_0033</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2010_11_0021 'Baráž o Extraligu' (L15, parent=NODE_S2010_11_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -33774,21 +34147,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NODE_S2010_11_0028</t>
+          <t>CLUB_S2010_11_0040</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2010_11_0028 'Baráž o I.ligu' (L25, parent=NODE_S2010_11_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -33796,24 +34167,662 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NODE_S2010_11_0043</t>
+          <t>CLUB_S2010_11_0049</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2010_11_0043 'O postup do I.ligy' (L25, parent=NODE_S2010_11_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0051</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0053</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0058</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0061</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0064</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0079</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0087</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0088</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0103</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Merend' → 'Nový Knín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0106</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0106</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0107</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0122</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0136</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0152</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0176</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0178</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0185</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0189</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0200</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0203</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0207</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0213</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0222</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0232</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2009_10_0117 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0233</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0234</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0241</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0253</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0030</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0031</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0032</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43288,6 +44297,11 @@
           <t>CLUB_S2010_11_0103</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V34" t="inlineStr">
         <is>
           <t>TR_S2010_11_00144</t>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -32,7 +32,7 @@
     <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12256,7 +12256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12328,7 +12328,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -12340,7 +12340,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12352,7 +12352,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12364,7 +12364,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12376,7 +12376,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -12388,7 +12388,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12400,7 +12400,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12412,7 +12412,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12424,7 +12424,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12436,7 +12436,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12448,7 +12448,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Merend' → 'Nový Knín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12460,7 +12460,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12472,7 +12472,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -12484,7 +12484,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12496,7 +12496,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12508,7 +12508,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12520,7 +12520,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Merend' → 'Nový Knín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12532,7 +12532,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12544,7 +12544,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12556,7 +12556,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -12568,7 +12568,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12580,7 +12580,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -12604,7 +12604,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -12616,7 +12616,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2009_10_0117 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -12628,7 +12628,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -12640,7 +12640,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -12650,9 +12650,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0030</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -12662,9 +12667,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0031</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -12674,147 +12684,17 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0032</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2009_10_0117 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>NODE_S2010_11_0030</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NODE_S2010_11_0031</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NODE_S2010_11_0032</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -12889,7 +12769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12948,6 +12828,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12990,6 +12875,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC Oceláři Třinec.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13037,6 +12927,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13079,6 +12974,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13121,6 +13021,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13163,6 +13068,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13205,6 +13115,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13247,6 +13162,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13289,6 +13209,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13331,6 +13256,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13373,6 +13303,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13415,6 +13350,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13457,6 +13397,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13499,6 +13444,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13541,6 +13491,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13583,6 +13538,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13625,6 +13585,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13667,6 +13632,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13709,6 +13679,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13751,6 +13726,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13793,6 +13773,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13835,6 +13820,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13877,6 +13867,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13919,6 +13914,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13961,6 +13961,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14003,6 +14008,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14045,6 +14055,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14087,6 +14102,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14129,6 +14149,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14176,6 +14201,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14208,6 +14238,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14240,6 +14275,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14314,6 +14354,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0032</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -14482,6 +14527,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0035</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14524,6 +14574,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0036</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14566,6 +14621,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0037</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14608,6 +14668,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0038</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14650,6 +14715,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0039</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14692,6 +14762,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0040</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14734,6 +14809,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0041</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14776,6 +14856,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0042</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14818,6 +14903,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0043</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14860,6 +14950,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0044</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14902,6 +14997,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0045</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14944,6 +15044,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0046</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14986,6 +15091,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0047</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15028,6 +15138,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0048</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -15070,6 +15185,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0049</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15112,6 +15232,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0050</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15154,6 +15279,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0051</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15196,6 +15326,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0052</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -15238,6 +15373,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0053</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15574,6 +15714,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0057</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -15616,6 +15761,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0058</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -15742,6 +15892,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0059</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -15784,6 +15939,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0060</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -15826,6 +15986,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0061</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -15868,6 +16033,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0062</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -15910,6 +16080,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0063</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -15952,6 +16127,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0064</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -15994,6 +16174,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0065</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -16246,6 +16431,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0071</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -16288,6 +16478,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0072</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -16412,6 +16607,11 @@
       <c r="K84" t="inlineStr">
         <is>
           <t>Kontejner L40</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S2009_10_0075</t>
         </is>
       </c>
     </row>
@@ -16435,6 +16635,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -16452,6 +16657,11 @@
           <t>NODE_S2010_11_0001</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -16469,6 +16679,11 @@
           <t>NODE_S2010_11_0003</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -16486,6 +16701,11 @@
           <t>NODE_S2010_11_0003</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -16503,6 +16723,11 @@
           <t>NODE_S2010_11_0037</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -16513,6 +16738,11 @@
       <c r="B93" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -24235,12 +24465,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -24571,12 +24801,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -24739,12 +24969,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -25638,12 +25868,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26347,12 +26577,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>SC Kolín</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -27454,12 +27684,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -28215,12 +28445,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -28257,12 +28487,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -32983,12 +33213,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33702,12 +33932,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -33958,7 +34188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -34032,12 +34262,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0006</t>
+          <t>CLUB_S2010_11_0015</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34052,12 +34282,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0014</t>
+          <t>CLUB_S2010_11_0024</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34072,12 +34302,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0015</t>
+          <t>CLUB_S2010_11_0033</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34092,12 +34322,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0018</t>
+          <t>CLUB_S2010_11_0049</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34112,12 +34342,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0024</t>
+          <t>CLUB_S2010_11_0051</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34132,12 +34362,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0033</t>
+          <t>CLUB_S2010_11_0053</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34152,12 +34382,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0040</t>
+          <t>CLUB_S2010_11_0058</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34172,12 +34402,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0049</t>
+          <t>CLUB_S2010_11_0064</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34192,12 +34422,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0051</t>
+          <t>CLUB_S2010_11_0079</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34212,12 +34442,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0053</t>
+          <t>CLUB_S2010_11_0087</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34232,12 +34462,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0058</t>
+          <t>CLUB_S2010_11_0103</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Merend' → 'Nový Knín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34252,12 +34482,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0061</t>
+          <t>CLUB_S2010_11_0106</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34272,12 +34502,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0064</t>
+          <t>CLUB_S2010_11_0122</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34292,12 +34522,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0079</t>
+          <t>CLUB_S2010_11_0136</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34312,12 +34542,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0087</t>
+          <t>CLUB_S2010_11_0152</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34332,12 +34562,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0088</t>
+          <t>CLUB_S2010_11_0176</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34352,12 +34582,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0103</t>
+          <t>CLUB_S2010_11_0178</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Merend' → 'Nový Knín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34372,12 +34602,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0106</t>
+          <t>CLUB_S2010_11_0185</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -34392,12 +34622,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0106</t>
+          <t>CLUB_S2010_11_0189</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34412,12 +34642,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0107</t>
+          <t>CLUB_S2010_11_0200</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -34432,12 +34662,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0122</t>
+          <t>CLUB_S2010_11_0203</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34452,12 +34682,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0136</t>
+          <t>CLUB_S2010_11_0207</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34472,12 +34702,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0152</t>
+          <t>CLUB_S2010_11_0213</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -34492,12 +34722,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0176</t>
+          <t>CLUB_S2010_11_0222</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -34512,12 +34742,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0178</t>
+          <t>CLUB_S2010_11_0232</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2009_10_0117 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -34532,12 +34762,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0185</t>
+          <t>CLUB_S2010_11_0233</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -34552,12 +34782,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0189</t>
+          <t>CLUB_S2010_11_0241</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -34567,17 +34797,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0200</t>
+          <t>NODE_S2010_11_0030</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
     </row>
@@ -34587,17 +34817,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0203</t>
+          <t>NODE_S2010_11_0031</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
     </row>
@@ -34607,222 +34837,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S2010_11_0207</t>
+          <t>NODE_S2010_11_0032</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S2010_11_0213</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S2010_11_0222</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S2010_11_0232</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2009_10_0117 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S2010_11_0233</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S2010_11_0234</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S2010_11_0241</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S2010_11_0253</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>NODE_S2010_11_0030</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>NODE_S2010_11_0031</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>NODE_S2010_11_0032</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F42"/>
+  <autoFilter ref="A1:F32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -12769,7 +12769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:N98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12833,6 +12833,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16615,8 +16625,6 @@
         </is>
       </c>
     </row>
-    <row r="85"/>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -16746,7 +16754,6 @@
         </is>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -13021,6 +13021,16 @@
           <t>NODE_S2010_11_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13035,6 +13045,14 @@
         <is>
           <t>NODE_S2009_10_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -13209,6 +13227,16 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13223,6 +13251,14 @@
         <is>
           <t>NODE_S2009_10_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -13303,6 +13339,16 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13317,6 +13363,14 @@
         <is>
           <t>NODE_S2009_10_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -13350,6 +13404,16 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13364,6 +13428,14 @@
         <is>
           <t>NODE_S2009_10_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -13397,6 +13469,8 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13411,6 +13485,14 @@
         <is>
           <t>NODE_S2009_10_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -13444,6 +13526,8 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13458,6 +13542,14 @@
         <is>
           <t>NODE_S2009_10_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -13491,6 +13583,8 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13505,6 +13599,14 @@
         <is>
           <t>NODE_S2009_10_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -13538,6 +13640,8 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13552,6 +13656,14 @@
         <is>
           <t>NODE_S2009_10_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -13585,6 +13697,8 @@
           <t>NODE_S2010_11_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13599,6 +13713,14 @@
         <is>
           <t>NODE_S2009_10_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -13632,6 +13754,8 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13646,6 +13770,14 @@
         <is>
           <t>NODE_S2009_10_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -13679,6 +13811,8 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13693,6 +13827,14 @@
         <is>
           <t>NODE_S2009_10_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -13726,6 +13868,16 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13740,6 +13892,14 @@
         <is>
           <t>NODE_S2009_10_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -13867,6 +14027,16 @@
           <t>NODE_S2010_11_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13881,6 +14051,14 @@
         <is>
           <t>NODE_S2009_10_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>32 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -13914,6 +14092,16 @@
           <t>NODE_S2010_11_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13928,6 +14116,14 @@
         <is>
           <t>NODE_S2009_10_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -13961,6 +14157,12 @@
           <t>NODE_S2010_11_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13975,6 +14177,14 @@
         <is>
           <t>NODE_S2009_10_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -14008,6 +14218,12 @@
           <t>NODE_S2010_11_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14022,6 +14238,14 @@
         <is>
           <t>NODE_S2009_10_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -14055,6 +14279,8 @@
           <t>NODE_S2010_11_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14069,6 +14295,14 @@
         <is>
           <t>NODE_S2009_10_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -14102,6 +14336,8 @@
           <t>NODE_S2010_11_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14116,6 +14352,14 @@
         <is>
           <t>NODE_S2009_10_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>28.–32. ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -14668,6 +14912,12 @@
           <t>NODE_S2010_11_0037</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0041</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14682,6 +14932,14 @@
         <is>
           <t>NODE_S2009_10_0038</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -14715,6 +14973,12 @@
           <t>NODE_S2010_11_0037</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0042</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14729,6 +14993,14 @@
         <is>
           <t>NODE_S2009_10_0039</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -14762,6 +15034,8 @@
           <t>NODE_S2010_11_0037</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14776,6 +15050,14 @@
         <is>
           <t>NODE_S2009_10_0040</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -14903,6 +15185,8 @@
           <t>NODE_S2010_11_0037</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14917,6 +15201,14 @@
         <is>
           <t>NODE_S2009_10_0043</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -15044,6 +15336,12 @@
           <t>NODE_S2010_11_0037</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0040</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15058,6 +15356,14 @@
         <is>
           <t>NODE_S2009_10_0046</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -15138,6 +15444,12 @@
           <t>NODE_S2010_11_0049</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0051</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15152,6 +15464,14 @@
         <is>
           <t>NODE_S2009_10_0048</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -15185,6 +15505,8 @@
           <t>NODE_S2010_11_0049</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15199,6 +15521,14 @@
         <is>
           <t>NODE_S2009_10_0049</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -15279,6 +15609,12 @@
           <t>NODE_S2010_11_0052</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0054</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15293,6 +15629,14 @@
         <is>
           <t>NODE_S2009_10_0051</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -15326,6 +15670,8 @@
           <t>NODE_S2010_11_0052</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15340,6 +15686,14 @@
         <is>
           <t>NODE_S2009_10_0052</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -15761,6 +16115,12 @@
           <t>NODE_S2010_11_0063</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0067</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15775,6 +16135,14 @@
         <is>
           <t>NODE_S2009_10_0058</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -15892,6 +16260,8 @@
           <t>NODE_S2010_11_0063</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15906,6 +16276,14 @@
         <is>
           <t>NODE_S2009_10_0059</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -15986,6 +16364,12 @@
           <t>NODE_S2010_11_0068</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0072</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16000,6 +16384,14 @@
         <is>
           <t>NODE_S2009_10_0061</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -16127,6 +16519,8 @@
           <t>NODE_S2010_11_0068</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16141,6 +16535,14 @@
         <is>
           <t>NODE_S2009_10_0064</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -16221,6 +16623,12 @@
           <t>NODE_S2010_11_0073</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0075</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16230,6 +16638,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -16263,6 +16679,8 @@
           <t>NODE_S2010_11_0073</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16272,6 +16690,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -16305,6 +16731,12 @@
           <t>NODE_S2010_11_0073</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0075</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16314,6 +16746,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -16347,6 +16787,8 @@
           <t>NODE_S2010_11_0073</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16356,6 +16798,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -16478,6 +16928,12 @@
           <t>NODE_S2010_11_0079</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0081</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16492,6 +16948,14 @@
         <is>
           <t>NODE_S2009_10_0072</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -16525,6 +16989,8 @@
           <t>NODE_S2010_11_0079</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16534,6 +17000,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -16567,6 +17041,8 @@
           <t>NODE_S2010_11_0079</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16576,6 +17052,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -16625,6 +17109,8 @@
         </is>
       </c>
     </row>
+    <row r="85"/>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -16754,6 +17240,7 @@
         </is>
       </c>
     </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -752,6 +752,11 @@
           <t>HC Oceláři Třinec (C)</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
@@ -13469,8 +13474,6 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13526,8 +13529,6 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13583,8 +13584,6 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13640,8 +13639,6 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13697,8 +13694,6 @@
           <t>NODE_S2010_11_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13754,8 +13749,6 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13811,8 +13804,6 @@
           <t>NODE_S2010_11_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14162,7 +14153,6 @@
           <t>NODE_S2010_11_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14223,7 +14213,6 @@
           <t>NODE_S2010_11_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14279,8 +14268,6 @@
           <t>NODE_S2010_11_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14336,8 +14323,6 @@
           <t>NODE_S2010_11_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14917,7 +14902,6 @@
           <t>NODE_S2010_11_0041</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14978,7 +14962,6 @@
           <t>NODE_S2010_11_0042</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15034,8 +15017,6 @@
           <t>NODE_S2010_11_0037</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15185,8 +15166,6 @@
           <t>NODE_S2010_11_0037</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15341,7 +15320,6 @@
           <t>NODE_S2010_11_0040</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15449,7 +15427,6 @@
           <t>NODE_S2010_11_0051</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15505,8 +15482,6 @@
           <t>NODE_S2010_11_0049</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15614,7 +15589,6 @@
           <t>NODE_S2010_11_0054</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15670,8 +15644,6 @@
           <t>NODE_S2010_11_0052</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16120,7 +16092,6 @@
           <t>NODE_S2010_11_0067</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16260,8 +16231,6 @@
           <t>NODE_S2010_11_0063</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16369,7 +16338,6 @@
           <t>NODE_S2010_11_0072</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16519,8 +16487,6 @@
           <t>NODE_S2010_11_0068</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16628,7 +16594,6 @@
           <t>NODE_S2010_11_0075</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16679,8 +16644,6 @@
           <t>NODE_S2010_11_0073</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16736,7 +16699,6 @@
           <t>NODE_S2010_11_0075</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16787,8 +16749,6 @@
           <t>NODE_S2010_11_0073</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16933,7 +16893,6 @@
           <t>NODE_S2010_11_0081</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16989,8 +16948,6 @@
           <t>NODE_S2010_11_0079</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17041,8 +16998,6 @@
           <t>NODE_S2010_11_0079</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17109,8 +17064,6 @@
         </is>
       </c>
     </row>
-    <row r="85"/>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -17240,7 +17193,6 @@
         </is>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
@@ -34488,7 +34440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34668,6 +34620,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Oceláři Třinec</t>
         </is>
       </c>
     </row>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -17064,6 +17064,8 @@
         </is>
       </c>
     </row>
+    <row r="85"/>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -17193,6 +17195,7 @@
         </is>
       </c>
     </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -8986,7 +8986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9697,6 +9697,523 @@
       <c r="V10" t="inlineStr">
         <is>
           <t>TR_S2010_11_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0256</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00315</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0257</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00316</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HC Janovice</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0258</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00317</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sokol Brtnice</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0259</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00318</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0260</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00319</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice-Brod</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0261</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00320</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0262</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00321</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0263</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00322</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0264</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00323</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0265</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00324</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>11</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0266</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00325</t>
         </is>
       </c>
     </row>
@@ -12774,7 +13291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N98"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17221,6 +17738,70 @@
       <c r="A98" t="inlineStr">
         <is>
           <t>II.liga: Západ/Střed/Východ + 8F/QF/SF/finále.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0084</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Karlovarský – Krajská Liga</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0085</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Vysočina – Jihlava</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0078</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -24613,7 +25194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J239"/>
+  <dimension ref="A1:J251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -34429,6 +35010,390 @@
       <c r="J239" t="inlineStr">
         <is>
           <t>Studénka</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0255</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>HC Tachov</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>HC Tachov</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>30KVRY</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0256</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0257</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0258</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>HC Janovice</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>HC Janovice</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0259</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Sokol Brtnice</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Sokol Brtnice</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0260</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0261</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice-Brod</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice-Brod</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0262</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0263</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0264</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0265</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0266</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>
@@ -50561,7 +51526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -52050,6 +53015,73 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Krajská Liga</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0084</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HC Tachov</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Krajská Liga</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0084</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2010_11_0255</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2010_11_00314</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -41,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +116,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -17581,8 +17592,6 @@
         </is>
       </c>
     </row>
-    <row r="85"/>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -17712,7 +17721,6 @@
         </is>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
@@ -35614,7 +35622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35671,7 +35679,7 @@
           <t>CLUB_S2010_11_0001</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35691,7 +35699,7 @@
           <t>CLUB_S2010_11_0015</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35711,7 +35719,7 @@
           <t>CLUB_S2010_11_0024</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35731,7 +35739,7 @@
           <t>CLUB_S2010_11_0033</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35751,7 +35759,7 @@
           <t>CLUB_S2010_11_0049</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -35771,7 +35779,7 @@
           <t>CLUB_S2010_11_0051</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35791,7 +35799,7 @@
           <t>CLUB_S2010_11_0053</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35811,7 +35819,7 @@
           <t>CLUB_S2010_11_0058</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35831,7 +35839,7 @@
           <t>CLUB_S2010_11_0064</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35851,7 +35859,7 @@
           <t>CLUB_S2010_11_0079</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35871,7 +35879,7 @@
           <t>CLUB_S2010_11_0087</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35891,7 +35899,7 @@
           <t>CLUB_S2010_11_0103</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Merend' → 'Nový Knín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -35911,7 +35919,7 @@
           <t>CLUB_S2010_11_0106</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35931,7 +35939,7 @@
           <t>CLUB_S2010_11_0122</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35951,7 +35959,7 @@
           <t>CLUB_S2010_11_0136</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35971,7 +35979,7 @@
           <t>CLUB_S2010_11_0152</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35991,7 +35999,7 @@
           <t>CLUB_S2010_11_0176</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -36011,7 +36019,7 @@
           <t>CLUB_S2010_11_0178</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -36031,7 +36039,7 @@
           <t>CLUB_S2010_11_0185</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -36051,7 +36059,7 @@
           <t>CLUB_S2010_11_0189</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -36071,7 +36079,7 @@
           <t>CLUB_S2010_11_0200</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -36091,7 +36099,7 @@
           <t>CLUB_S2010_11_0203</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -36111,7 +36119,7 @@
           <t>CLUB_S2010_11_0207</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -36131,7 +36139,7 @@
           <t>CLUB_S2010_11_0213</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -36151,7 +36159,7 @@
           <t>CLUB_S2010_11_0222</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -36171,7 +36179,7 @@
           <t>CLUB_S2010_11_0232</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2009_10_0117 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -36191,7 +36199,7 @@
           <t>CLUB_S2010_11_0233</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
@@ -36211,7 +36219,7 @@
           <t>CLUB_S2010_11_0241</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
@@ -36231,7 +36239,7 @@
           <t>NODE_S2010_11_0030</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
@@ -36251,7 +36259,7 @@
           <t>NODE_S2010_11_0031</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
@@ -36271,11 +36279,63 @@
           <t>NODE_S2010_11_0032</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>KVAL  skupina B (celostátní) · NODE_S2010_11_0031</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (SK Kadaň B (UST), HC Slavoj Velké Popovice (STČ)), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Karlovarský – Krajská Liga · NODE_S2010_11_0084</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC Tachov), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F32"/>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +118,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12789,7 +12792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13228,6 +13231,40 @@
         </is>
       </c>
       <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0031</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (SK Kadaň B (UST), HC Slavoj Velké Popovice (STČ)), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0084</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC Tachov), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -36299,7 +36336,7 @@
           <t>KVAL  skupina B (celostátní) · NODE_S2010_11_0031</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (SK Kadaň B (UST), HC Slavoj Velké Popovice (STČ)), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -36325,7 +36362,7 @@
           <t>Karlovarský – Krajská Liga · NODE_S2010_11_0084</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC Tachov), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -15019,7 +15019,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KVAL  skupina A</t>
+          <t>KVAL skupina A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KVAL  skupina B</t>
+          <t>KVAL skupina B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KVAL  skupina C</t>
+          <t>KVAL skupina C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Praha L40 základní část</t>
+          <t>Praha, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -16024,7 +16024,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Finále</t>
+          <t>Středočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Finále</t>
+          <t>Jihočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -16288,7 +16288,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina A</t>
+          <t>Plzeňský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina B</t>
+          <t>Plzeňský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina C</t>
+          <t>Plzeňský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -16456,7 +16456,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40 skupina Green</t>
+          <t>Karlovarský, 4. úroveň, skupina Green</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40 skupina Blue</t>
+          <t>Karlovarský, 4. úroveň, skupina Blue</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 základní část</t>
+          <t>Liberecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 skupina A</t>
+          <t>Liberecký, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 skupina B</t>
+          <t>Liberecký, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 Finále</t>
+          <t>Liberecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -16875,7 +16875,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 základní část</t>
+          <t>Hradecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -16935,7 +16935,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina A</t>
+          <t>Hradecký, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina B</t>
+          <t>Hradecký, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -17029,7 +17029,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 Finále</t>
+          <t>Hradecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -17131,7 +17131,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 základní část</t>
+          <t>Pardubický, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -17236,7 +17236,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 základní část</t>
+          <t>Pardubický, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -17341,7 +17341,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -17383,7 +17383,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 základní část</t>
+          <t>Jihomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -17590,7 +17590,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -17629,6 +17629,8 @@
         </is>
       </c>
     </row>
+    <row r="85"/>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -17661,7 +17663,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -17758,6 +17760,7 @@
         </is>
       </c>
     </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>

--- a/data/S2010_11_FINAL.xlsx
+++ b/data/S2010_11_FINAL.xlsx
@@ -824,7 +824,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -17629,8 +17629,6 @@
         </is>
       </c>
     </row>
-    <row r="85"/>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -17760,7 +17758,6 @@
         </is>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
@@ -18156,7 +18153,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -18234,7 +18231,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -18312,7 +18309,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -18390,7 +18387,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -18468,7 +18465,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -18546,7 +18543,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -18624,7 +18621,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -18702,7 +18699,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -18780,7 +18777,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -18858,7 +18855,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -18936,7 +18933,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -19014,7 +19011,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -19092,7 +19089,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -19170,7 +19167,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -19253,7 +19250,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -19336,7 +19333,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -19414,7 +19411,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -19492,7 +19489,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -19570,7 +19567,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -19648,7 +19645,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -19726,7 +19723,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -19804,7 +19801,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -19882,7 +19879,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -19960,7 +19957,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -20038,7 +20035,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -20116,7 +20113,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -20194,7 +20191,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -20272,7 +20269,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -20350,7 +20347,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -20428,7 +20425,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -20506,7 +20503,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -20584,7 +20581,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -21199,7 +21196,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -21277,7 +21274,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -21511,7 +21508,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
